--- a/data/raw/GLNPO 2024 Spring/Superior/D20/Zoops/SU 08M D20 QA Spring 2024 24GS01I54 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Superior/D20/Zoops/SU 08M D20 QA Spring 2024 24GS01I54 Zoop.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Superior\D20\Zoops\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Superior\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12F7419D-25FE-4CD0-BD65-12DAC02232EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6D24BB-0132-40CA-80AB-C00C18660106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{B22FB38C-D243-44C5-8235-7B4B8CE20899}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B22FB38C-D243-44C5-8235-7B4B8CE20899}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="15" r:id="rId2"/>
+    <pivotCache cacheId="22" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1705" uniqueCount="65">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -180,9 +180,6 @@
   </si>
   <si>
     <t>SENCOPE</t>
-  </si>
-  <si>
-    <t>CALIM</t>
   </si>
   <si>
     <t>C</t>
@@ -2831,7 +2828,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{037E719B-7B72-4FF8-847D-28EA73A374C9}" name="PivotTable1" cacheId="15" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{037E719B-7B72-4FF8-847D-28EA73A374C9}" name="PivotTable1" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:X12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -3249,18 +3246,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83750C3E-14A9-4A75-A39C-FCB8FA9C5FB9}">
   <dimension ref="A1:X128"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="25.28515625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.85546875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="6.28515625" customWidth="1"/>
-    <col min="23" max="23" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="25.33203125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.33203125" customWidth="1"/>
+    <col min="23" max="23" width="2.44140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3316,18 +3313,18 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
         <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E2" t="s">
         <v>19</v>
@@ -3369,18 +3366,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>19</v>
@@ -3422,24 +3419,24 @@
         <v>1</v>
       </c>
       <c r="T3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
         <v>18</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
         <v>19</v>
@@ -3481,33 +3478,33 @@
         <v>1</v>
       </c>
       <c r="T4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="U4" t="s">
+        <v>19</v>
+      </c>
+      <c r="V4" t="s">
+        <v>46</v>
+      </c>
+      <c r="W4" t="s">
+        <v>47</v>
+      </c>
+      <c r="X4" t="s">
         <v>49</v>
       </c>
-      <c r="U4" t="s">
-        <v>19</v>
-      </c>
-      <c r="V4" t="s">
-        <v>47</v>
-      </c>
-      <c r="W4" t="s">
-        <v>48</v>
-      </c>
-      <c r="X4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
         <v>18</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" t="s">
         <v>19</v>
@@ -3558,18 +3555,18 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
         <v>18</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E6" t="s">
         <v>19</v>
@@ -3620,18 +3617,18 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
         <v>18</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>19</v>
@@ -3685,18 +3682,18 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
         <v>18</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E8" t="s">
         <v>19</v>
@@ -3747,18 +3744,18 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
         <v>18</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>19</v>
@@ -3809,18 +3806,18 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
         <v>18</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E10" t="s">
         <v>19</v>
@@ -3877,18 +3874,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>19</v>
@@ -3942,18 +3939,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
         <v>19</v>
@@ -3995,7 +3992,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="U12">
         <v>302</v>
@@ -4010,18 +4007,18 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E13" t="s">
         <v>19</v>
@@ -4063,18 +4060,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
         <v>18</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E14" t="s">
         <v>19</v>
@@ -4116,18 +4113,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
         <v>18</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>19</v>
@@ -4169,23 +4166,23 @@
         <v>1</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
         <v>18</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E16" t="s">
         <v>19</v>
@@ -4227,27 +4224,27 @@
         <v>1</v>
       </c>
       <c r="T16" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="U16" s="5" t="s">
         <v>54</v>
-      </c>
-      <c r="U16" s="5" t="s">
-        <v>55</v>
       </c>
       <c r="V16" s="6">
         <v>0.997</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E17" t="s">
         <v>19</v>
@@ -4290,24 +4287,24 @@
       </c>
       <c r="T17" s="4"/>
       <c r="U17" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V17" s="6">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
         <v>18</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E18" t="s">
         <v>19</v>
@@ -4349,27 +4346,27 @@
         <v>1</v>
       </c>
       <c r="T18" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="U18" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V18" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
         <v>18</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E19" t="s">
         <v>19</v>
@@ -4412,24 +4409,24 @@
       </c>
       <c r="T19" s="4"/>
       <c r="U19" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="V19" s="5">
         <v>0.996</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
         <v>18</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E20" t="s">
         <v>19</v>
@@ -4471,25 +4468,25 @@
         <v>1</v>
       </c>
       <c r="T20" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="U20" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="U20" s="5" t="s">
-        <v>58</v>
-      </c>
       <c r="V20" s="5"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B21" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
         <v>18</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E21" t="s">
         <v>19</v>
@@ -4531,25 +4528,25 @@
         <v>1</v>
       </c>
       <c r="T21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="U21" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="U21" s="5" t="s">
-        <v>60</v>
-      </c>
       <c r="V21" s="5"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
         <v>18</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E22" t="s">
         <v>19</v>
@@ -4591,25 +4588,25 @@
         <v>1</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="U22" s="5"/>
       <c r="V22" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
         <v>18</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E23" t="s">
         <v>19</v>
@@ -4651,18 +4648,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C24" t="s">
         <v>18</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s">
         <v>19</v>
@@ -4704,18 +4701,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B25" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C25" t="s">
         <v>18</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E25" t="s">
         <v>19</v>
@@ -4757,18 +4754,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E26" t="s">
         <v>19</v>
@@ -4810,18 +4807,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C27" t="s">
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E27" t="s">
         <v>19</v>
@@ -4863,18 +4860,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B28" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C28" t="s">
         <v>18</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E28" t="s">
         <v>19</v>
@@ -4916,18 +4913,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B29" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
         <v>18</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E29" t="s">
         <v>19</v>
@@ -4969,18 +4966,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C30" t="s">
         <v>18</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" t="s">
         <v>19</v>
@@ -5022,18 +5019,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C31" t="s">
         <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E31" t="s">
         <v>19</v>
@@ -5075,18 +5072,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" t="s">
         <v>18</v>
       </c>
       <c r="D32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E32" t="s">
         <v>19</v>
@@ -5128,18 +5125,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" t="s">
         <v>18</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E33" t="s">
         <v>19</v>
@@ -5181,18 +5178,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" t="s">
         <v>18</v>
       </c>
       <c r="D34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E34" t="s">
         <v>19</v>
@@ -5234,18 +5231,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C35" t="s">
         <v>18</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E35" t="s">
         <v>19</v>
@@ -5287,18 +5284,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C36" t="s">
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E36" t="s">
         <v>19</v>
@@ -5340,18 +5337,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C37" t="s">
         <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E37" t="s">
         <v>19</v>
@@ -5393,18 +5390,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C38" t="s">
         <v>18</v>
       </c>
       <c r="D38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E38" t="s">
         <v>19</v>
@@ -5446,18 +5443,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C39" t="s">
         <v>18</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E39" t="s">
         <v>19</v>
@@ -5499,18 +5496,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C40" t="s">
         <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E40" t="s">
         <v>19</v>
@@ -5552,18 +5549,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C41" t="s">
         <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E41" t="s">
         <v>19</v>
@@ -5605,18 +5602,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C42" t="s">
         <v>18</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E42" t="s">
         <v>19</v>
@@ -5658,18 +5655,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B43" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C43" t="s">
         <v>18</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E43" t="s">
         <v>19</v>
@@ -5711,18 +5708,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B44" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C44" t="s">
         <v>18</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E44" t="s">
         <v>19</v>
@@ -5764,18 +5761,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C45" t="s">
         <v>18</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E45" t="s">
         <v>19</v>
@@ -5817,18 +5814,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C46" t="s">
         <v>18</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" t="s">
         <v>19</v>
@@ -5870,18 +5867,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C47" t="s">
         <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E47" t="s">
         <v>19</v>
@@ -5923,18 +5920,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" t="s">
         <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E48" t="s">
         <v>19</v>
@@ -5976,18 +5973,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B49" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C49" t="s">
         <v>18</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E49" t="s">
         <v>19</v>
@@ -6029,18 +6026,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C50" t="s">
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E50" t="s">
         <v>19</v>
@@ -6082,18 +6079,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C51" t="s">
         <v>18</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E51" t="s">
         <v>19</v>
@@ -6135,18 +6132,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C52" t="s">
         <v>18</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E52" t="s">
         <v>19</v>
@@ -6188,18 +6185,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C53" t="s">
         <v>18</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E53" t="s">
         <v>19</v>
@@ -6241,18 +6238,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B54" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C54" t="s">
         <v>18</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E54" t="s">
         <v>19</v>
@@ -6294,18 +6291,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C55" t="s">
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E55" t="s">
         <v>19</v>
@@ -6347,18 +6344,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B56" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C56" t="s">
         <v>18</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E56" t="s">
         <v>19</v>
@@ -6385,7 +6382,7 @@
         <v>45</v>
       </c>
       <c r="M56" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="N56" t="s">
         <v>39</v>
@@ -6400,18 +6397,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C57" t="s">
         <v>18</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E57" t="s">
         <v>19</v>
@@ -6453,18 +6450,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C58" t="s">
         <v>18</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E58" t="s">
         <v>19</v>
@@ -6506,18 +6503,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B59" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C59" t="s">
         <v>18</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E59" t="s">
         <v>19</v>
@@ -6559,18 +6556,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B60" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C60" t="s">
         <v>18</v>
       </c>
       <c r="D60" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E60" t="s">
         <v>19</v>
@@ -6612,18 +6609,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C61" t="s">
         <v>18</v>
       </c>
       <c r="D61" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E61" t="s">
         <v>19</v>
@@ -6665,18 +6662,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B62" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C62" t="s">
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E62" t="s">
         <v>19</v>
@@ -6718,18 +6715,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C63" t="s">
         <v>18</v>
       </c>
       <c r="D63" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E63" t="s">
         <v>19</v>
@@ -6771,18 +6768,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C64" t="s">
         <v>18</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E64" t="s">
         <v>19</v>
@@ -6824,18 +6821,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C65" t="s">
         <v>18</v>
       </c>
       <c r="D65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E65" t="s">
         <v>19</v>
@@ -6877,18 +6874,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C66" t="s">
         <v>18</v>
       </c>
       <c r="D66" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E66" t="s">
         <v>19</v>
@@ -6930,18 +6927,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C67" t="s">
         <v>18</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E67" t="s">
         <v>19</v>
@@ -6983,18 +6980,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B68" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C68" t="s">
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E68" t="s">
         <v>19</v>
@@ -7036,18 +7033,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B69" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C69" t="s">
         <v>18</v>
       </c>
       <c r="D69" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E69" t="s">
         <v>19</v>
@@ -7089,18 +7086,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B70" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C70" t="s">
         <v>18</v>
       </c>
       <c r="D70" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E70" t="s">
         <v>19</v>
@@ -7142,18 +7139,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B71" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C71" t="s">
         <v>18</v>
       </c>
       <c r="D71" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E71" t="s">
         <v>19</v>
@@ -7195,18 +7192,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C72" t="s">
         <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E72" t="s">
         <v>19</v>
@@ -7233,7 +7230,7 @@
         <v>45</v>
       </c>
       <c r="M72" t="s">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="N72" t="s">
         <v>39</v>
@@ -7248,18 +7245,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B73" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C73" t="s">
         <v>18</v>
       </c>
       <c r="D73" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E73" t="s">
         <v>19</v>
@@ -7301,18 +7298,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B74" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C74" t="s">
         <v>18</v>
       </c>
       <c r="D74" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E74" t="s">
         <v>19</v>
@@ -7354,18 +7351,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B75" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C75" t="s">
         <v>18</v>
       </c>
       <c r="D75" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E75" t="s">
         <v>19</v>
@@ -7407,18 +7404,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B76" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C76" t="s">
         <v>18</v>
       </c>
       <c r="D76" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E76" t="s">
         <v>19</v>
@@ -7460,18 +7457,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C77" t="s">
         <v>18</v>
       </c>
       <c r="D77" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E77" t="s">
         <v>19</v>
@@ -7513,18 +7510,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C78" t="s">
         <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E78" t="s">
         <v>19</v>
@@ -7566,18 +7563,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B79" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C79" t="s">
         <v>18</v>
       </c>
       <c r="D79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E79" t="s">
         <v>19</v>
@@ -7619,18 +7616,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B80" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C80" t="s">
         <v>18</v>
       </c>
       <c r="D80" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E80" t="s">
         <v>19</v>
@@ -7672,18 +7669,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B81" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C81" t="s">
         <v>18</v>
       </c>
       <c r="D81" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E81" t="s">
         <v>19</v>
@@ -7725,18 +7722,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B82" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C82" t="s">
         <v>18</v>
       </c>
       <c r="D82" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
@@ -7778,18 +7775,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B83" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C83" t="s">
         <v>18</v>
       </c>
       <c r="D83" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
@@ -7831,18 +7828,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B84" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C84" t="s">
         <v>18</v>
       </c>
       <c r="D84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E84" t="s">
         <v>19</v>
@@ -7884,18 +7881,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B85" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C85" t="s">
         <v>18</v>
       </c>
       <c r="D85" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E85" t="s">
         <v>19</v>
@@ -7937,18 +7934,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B86" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C86" t="s">
         <v>18</v>
       </c>
       <c r="D86" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E86" t="s">
         <v>19</v>
@@ -7990,18 +7987,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B87" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C87" t="s">
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E87" t="s">
         <v>19</v>
@@ -8043,18 +8040,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B88" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C88" t="s">
         <v>18</v>
       </c>
       <c r="D88" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E88" t="s">
         <v>19</v>
@@ -8096,18 +8093,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B89" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C89" t="s">
         <v>18</v>
       </c>
       <c r="D89" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E89" t="s">
         <v>19</v>
@@ -8149,18 +8146,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B90" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C90" t="s">
         <v>18</v>
       </c>
       <c r="D90" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E90" t="s">
         <v>19</v>
@@ -8202,18 +8199,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B91" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C91" t="s">
         <v>18</v>
       </c>
       <c r="D91" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E91" t="s">
         <v>19</v>
@@ -8255,18 +8252,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B92" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C92" t="s">
         <v>18</v>
       </c>
       <c r="D92" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E92" t="s">
         <v>19</v>
@@ -8308,18 +8305,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B93" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C93" t="s">
         <v>18</v>
       </c>
       <c r="D93" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E93" t="s">
         <v>19</v>
@@ -8361,18 +8358,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B94" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C94" t="s">
         <v>18</v>
       </c>
       <c r="D94" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E94" t="s">
         <v>19</v>
@@ -8414,18 +8411,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B95" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C95" t="s">
         <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E95" t="s">
         <v>19</v>
@@ -8467,18 +8464,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B96" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C96" t="s">
         <v>18</v>
       </c>
       <c r="D96" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E96" t="s">
         <v>19</v>
@@ -8520,18 +8517,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B97" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C97" t="s">
         <v>18</v>
       </c>
       <c r="D97" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E97" t="s">
         <v>19</v>
@@ -8573,18 +8570,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B98" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C98" t="s">
         <v>18</v>
       </c>
       <c r="D98" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E98" t="s">
         <v>19</v>
@@ -8626,18 +8623,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B99" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C99" t="s">
         <v>18</v>
       </c>
       <c r="D99" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E99" t="s">
         <v>19</v>
@@ -8679,18 +8676,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B100" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C100" t="s">
         <v>18</v>
       </c>
       <c r="D100" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E100" t="s">
         <v>19</v>
@@ -8732,18 +8729,18 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B101" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C101" t="s">
         <v>18</v>
       </c>
       <c r="D101" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E101" t="s">
         <v>19</v>
@@ -8785,18 +8782,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B102" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C102" t="s">
         <v>18</v>
       </c>
       <c r="D102" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E102" t="s">
         <v>19</v>
@@ -8838,18 +8835,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C103" t="s">
         <v>18</v>
       </c>
       <c r="D103" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E103" t="s">
         <v>19</v>
@@ -8891,18 +8888,18 @@
         <v>55</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B104" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C104" t="s">
         <v>18</v>
       </c>
       <c r="D104" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E104" t="s">
         <v>19</v>
@@ -8944,18 +8941,18 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B105" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C105" t="s">
         <v>18</v>
       </c>
       <c r="D105" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E105" t="s">
         <v>19</v>
@@ -8997,18 +8994,18 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B106" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C106" t="s">
         <v>18</v>
       </c>
       <c r="D106" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E106" t="s">
         <v>19</v>
@@ -9050,21 +9047,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B107" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C107" t="s">
         <v>18</v>
       </c>
       <c r="D107" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E107" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F107">
         <v>8</v>
@@ -9103,21 +9100,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B108" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C108" t="s">
         <v>18</v>
       </c>
       <c r="D108" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E108" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F108">
         <v>8</v>
@@ -9156,21 +9153,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B109" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C109" t="s">
         <v>18</v>
       </c>
       <c r="D109" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E109" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F109">
         <v>8</v>
@@ -9209,21 +9206,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B110" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C110" t="s">
         <v>18</v>
       </c>
       <c r="D110" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E110" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F110">
         <v>8</v>
@@ -9262,21 +9259,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B111" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C111" t="s">
         <v>18</v>
       </c>
       <c r="D111" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E111" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F111">
         <v>8</v>
@@ -9315,21 +9312,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B112" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C112" t="s">
         <v>18</v>
       </c>
       <c r="D112" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E112" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F112">
         <v>8</v>
@@ -9368,21 +9365,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B113" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C113" t="s">
         <v>18</v>
       </c>
       <c r="D113" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E113" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F113">
         <v>8</v>
@@ -9421,21 +9418,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B114" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C114" t="s">
         <v>18</v>
       </c>
       <c r="D114" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F114">
         <v>8</v>
@@ -9474,21 +9471,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B115" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C115" t="s">
         <v>18</v>
       </c>
       <c r="D115" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E115" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F115">
         <v>8</v>
@@ -9527,21 +9524,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B116" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C116" t="s">
         <v>18</v>
       </c>
       <c r="D116" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F116">
         <v>8</v>
@@ -9580,21 +9577,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B117" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C117" t="s">
         <v>18</v>
       </c>
       <c r="D117" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E117" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F117">
         <v>8</v>
@@ -9633,21 +9630,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B118" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C118" t="s">
         <v>18</v>
       </c>
       <c r="D118" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E118" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F118">
         <v>8</v>
@@ -9686,21 +9683,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B119" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C119" t="s">
         <v>18</v>
       </c>
       <c r="D119" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E119" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F119">
         <v>8</v>
@@ -9739,21 +9736,21 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B120" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C120" t="s">
         <v>18</v>
       </c>
       <c r="D120" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E120" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F120">
         <v>4</v>
@@ -9792,21 +9789,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B121" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C121" t="s">
         <v>18</v>
       </c>
       <c r="D121" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E121" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F121">
         <v>4</v>
@@ -9845,21 +9842,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B122" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C122" t="s">
         <v>18</v>
       </c>
       <c r="D122" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E122" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F122">
         <v>4</v>
@@ -9898,21 +9895,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B123" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C123" t="s">
         <v>18</v>
       </c>
       <c r="D123" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E123" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F123">
         <v>4</v>
@@ -9951,21 +9948,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B124" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C124" t="s">
         <v>18</v>
       </c>
       <c r="D124" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E124" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F124">
         <v>4</v>
@@ -10004,21 +10001,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B125" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C125" t="s">
         <v>18</v>
       </c>
       <c r="D125" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E125" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F125">
         <v>4</v>
@@ -10057,21 +10054,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B126" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C126" t="s">
         <v>18</v>
       </c>
       <c r="D126" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E126" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F126">
         <v>4</v>
@@ -10110,21 +10107,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B127" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C127" t="s">
         <v>18</v>
       </c>
       <c r="D127" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E127" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F127">
         <v>4</v>
@@ -10163,21 +10160,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B128" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
       </c>
       <c r="D128" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E128" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F128">
         <v>4</v>

--- a/data/raw/GLNPO 2024 Spring/Superior/D20/Zoops/SU 08M D20 QA Spring 2024 24GS01I54 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Superior/D20/Zoops/SU 08M D20 QA Spring 2024 24GS01I54 Zoop.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Superior\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F6D24BB-0132-40CA-80AB-C00C18660106}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20D58253-D94F-420F-B41B-771F53F13F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B22FB38C-D243-44C5-8235-7B4B8CE20899}"/>
+    <workbookView xWindow="-1992" yWindow="2028" windowWidth="17280" windowHeight="8880" xr2:uid="{B22FB38C-D243-44C5-8235-7B4B8CE20899}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="22" r:id="rId2"/>
+    <pivotCache cacheId="16" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2828,7 +2828,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{037E719B-7B72-4FF8-847D-28EA73A374C9}" name="PivotTable1" cacheId="22" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{037E719B-7B72-4FF8-847D-28EA73A374C9}" name="PivotTable1" cacheId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T3:X12" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="17">
     <pivotField showAll="0"/>
@@ -3245,6 +3245,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83750C3E-14A9-4A75-A39C-FCB8FA9C5FB9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:X128"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -3313,7 +3314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>63</v>
       </c>
@@ -3366,7 +3367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>63</v>
       </c>
@@ -3425,7 +3426,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>63</v>
       </c>
@@ -3493,7 +3494,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>63</v>
       </c>
@@ -3555,7 +3556,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>63</v>
       </c>
@@ -3617,7 +3618,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>63</v>
       </c>
@@ -3682,7 +3683,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>63</v>
       </c>
@@ -3744,7 +3745,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>63</v>
       </c>
@@ -3806,7 +3807,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -3874,7 +3875,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -3939,7 +3940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>63</v>
       </c>
@@ -4007,7 +4008,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>63</v>
       </c>
@@ -4060,7 +4061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>63</v>
       </c>
@@ -4113,7 +4114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>63</v>
       </c>
@@ -4171,7 +4172,7 @@
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>63</v>
       </c>
@@ -4233,7 +4234,7 @@
         <v>0.997</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>63</v>
       </c>
@@ -4293,7 +4294,7 @@
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>63</v>
       </c>
@@ -4355,7 +4356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -4415,7 +4416,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>63</v>
       </c>
@@ -4475,7 +4476,7 @@
       </c>
       <c r="V20" s="5"/>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>63</v>
       </c>
@@ -4535,7 +4536,7 @@
       </c>
       <c r="V21" s="5"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>63</v>
       </c>
@@ -4595,7 +4596,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -4648,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>63</v>
       </c>
@@ -4701,7 +4702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>63</v>
       </c>
@@ -4754,7 +4755,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -4807,7 +4808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>63</v>
       </c>
@@ -4860,7 +4861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>63</v>
       </c>
@@ -4913,7 +4914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>63</v>
       </c>
@@ -4966,7 +4967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>63</v>
       </c>
@@ -5019,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>63</v>
       </c>
@@ -5072,7 +5073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:22" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>63</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>63</v>
       </c>
@@ -5178,7 +5179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>63</v>
       </c>
@@ -5231,7 +5232,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>63</v>
       </c>
@@ -5284,7 +5285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>63</v>
       </c>
@@ -5337,7 +5338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>63</v>
       </c>
@@ -5390,7 +5391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>63</v>
       </c>
@@ -5443,7 +5444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>63</v>
       </c>
@@ -5496,7 +5497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>63</v>
       </c>
@@ -5549,7 +5550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>63</v>
       </c>
@@ -5602,7 +5603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>63</v>
       </c>
@@ -5655,7 +5656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>63</v>
       </c>
@@ -5708,7 +5709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>63</v>
       </c>
@@ -5761,7 +5762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>63</v>
       </c>
@@ -5814,7 +5815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>63</v>
       </c>
@@ -5867,7 +5868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -5920,7 +5921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>63</v>
       </c>
@@ -5973,7 +5974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>63</v>
       </c>
@@ -6026,7 +6027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -6079,7 +6080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>63</v>
       </c>
@@ -6132,7 +6133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>63</v>
       </c>
@@ -6185,7 +6186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>63</v>
       </c>
@@ -6238,7 +6239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>63</v>
       </c>
@@ -6291,7 +6292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>63</v>
       </c>
@@ -6385,7 +6386,7 @@
         <v>30</v>
       </c>
       <c r="N56" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O56">
         <v>1.47</v>
@@ -6397,7 +6398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>63</v>
       </c>
@@ -6450,7 +6451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>63</v>
       </c>
@@ -6503,7 +6504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>63</v>
       </c>
@@ -6556,7 +6557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -6609,7 +6610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -6662,7 +6663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -6715,7 +6716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>63</v>
       </c>
@@ -6768,7 +6769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>63</v>
       </c>
@@ -6821,7 +6822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>63</v>
       </c>
@@ -6874,7 +6875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>63</v>
       </c>
@@ -6927,7 +6928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>63</v>
       </c>
@@ -6980,7 +6981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>63</v>
       </c>
@@ -7033,7 +7034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>63</v>
       </c>
@@ -7086,7 +7087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>63</v>
       </c>
@@ -7139,7 +7140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>63</v>
       </c>
@@ -7233,7 +7234,7 @@
         <v>30</v>
       </c>
       <c r="N72" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="O72">
         <v>1.4339999999999999</v>
@@ -7245,7 +7246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>63</v>
       </c>
@@ -7298,7 +7299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>63</v>
       </c>
@@ -7351,7 +7352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>63</v>
       </c>
@@ -7404,7 +7405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>63</v>
       </c>
@@ -7457,7 +7458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>63</v>
       </c>
@@ -7510,7 +7511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>63</v>
       </c>
@@ -7563,7 +7564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>63</v>
       </c>
@@ -7616,7 +7617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>63</v>
       </c>
@@ -7669,7 +7670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>63</v>
       </c>
@@ -7722,7 +7723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>63</v>
       </c>
@@ -7775,7 +7776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>63</v>
       </c>
@@ -7828,7 +7829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>63</v>
       </c>
@@ -7881,7 +7882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>63</v>
       </c>
@@ -7934,7 +7935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>63</v>
       </c>
@@ -7987,7 +7988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>63</v>
       </c>
@@ -8040,7 +8041,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>63</v>
       </c>
@@ -8093,7 +8094,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>63</v>
       </c>
@@ -8146,7 +8147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>63</v>
       </c>
@@ -8199,7 +8200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>63</v>
       </c>
@@ -8252,7 +8253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>63</v>
       </c>
@@ -8305,7 +8306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>63</v>
       </c>
@@ -8358,7 +8359,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>63</v>
       </c>
@@ -8411,7 +8412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>63</v>
       </c>
@@ -8464,7 +8465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>63</v>
       </c>
@@ -8517,7 +8518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>63</v>
       </c>
@@ -8570,7 +8571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>63</v>
       </c>
@@ -8623,7 +8624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>63</v>
       </c>
@@ -8676,7 +8677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>63</v>
       </c>
@@ -8729,7 +8730,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>63</v>
       </c>
@@ -8782,7 +8783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>63</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>63</v>
       </c>
@@ -8888,7 +8889,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>63</v>
       </c>
@@ -8941,7 +8942,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>63</v>
       </c>
@@ -8994,7 +8995,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>63</v>
       </c>
@@ -9100,7 +9101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>63</v>
       </c>
@@ -9153,7 +9154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>63</v>
       </c>
@@ -9206,7 +9207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>63</v>
       </c>
@@ -9259,7 +9260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>63</v>
       </c>
@@ -9312,7 +9313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>63</v>
       </c>
@@ -9365,7 +9366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>63</v>
       </c>
@@ -9471,7 +9472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>63</v>
       </c>
@@ -9577,7 +9578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>63</v>
       </c>
@@ -9630,7 +9631,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>63</v>
       </c>
@@ -9683,7 +9684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>63</v>
       </c>
@@ -9736,7 +9737,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>63</v>
       </c>
@@ -9789,7 +9790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>63</v>
       </c>
@@ -9842,7 +9843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>63</v>
       </c>
@@ -9895,7 +9896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>63</v>
       </c>
@@ -9948,7 +9949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>63</v>
       </c>
@@ -10001,7 +10002,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>63</v>
       </c>
@@ -10054,7 +10055,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>63</v>
       </c>
@@ -10107,7 +10108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>63</v>
       </c>
@@ -10160,7 +10161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>63</v>
       </c>
@@ -10214,6 +10215,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R128" xr:uid="{83750C3E-14A9-4A75-A39C-FCB8FA9C5FB9}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="Senecella copepodites"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
